--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-01_users_ユーザー_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-01_users_ユーザー_テーブル詳細設計書.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち users を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.1 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
 章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
         </is>
       </c>
@@ -746,7 +746,7 @@
       <c r="J2" s="9" t="n"/>
       <c r="K2" s="10" t="n"/>
     </row>
-    <row r="3" ht="48.5" customHeight="1">
+    <row r="3" ht="63" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>前提</t>
@@ -754,8 +754,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>dev の初期ユーザー4名（DevDataInitializer が userRepository.count() = 0 のときだけ作成。全員 hire_date=2024-04-01、status=ACTIVE）。パスワードハッシュは $2a$10$... のダミー。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>dev の初期ユーザー（DevDataInitializer が 100 名を userRepository.count() = 0 かつ seed-password 設定時だけ作成）のうち代表 4 名。全員 hire_date=2024-04-01、status=ACTIVE。パスワードハッシュは $2a$10$... のダミー。failed_login_count=0・locked_until=NULL・must_change_password=FALSE・password_changed_at=NULL は DB の既定値のため INSERT に含めない。
+例の INSERT は V1 適用直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>1（人事部）</t>
+          <t>1（管理部）</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -883,7 +883,7 @@
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="10" t="n"/>
     </row>
-    <row r="8" ht="19.5" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>2</t>
@@ -911,7 +911,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>2（営業部）</t>
+          <t>2（システム開発事業部）</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -932,7 +932,7 @@
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="10" t="n"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>3</t>
@@ -960,7 +960,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>2（営業部）</t>
+          <t>2（システム開発事業部）</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -981,7 +981,7 @@
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="n"/>
     </row>
-    <row r="10" ht="19.5" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>2（営業部）</t>
+          <t>2（システム開発事業部）</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO users(email,password_hash,name,role,department_id,manager_id,hire_date,status) VALUES ('admin@example.com','$2a$10$DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD','人事 管理者','ADMIN',(SELECT id FROM departments WHERE name='人事部'),NULL,DATE '2024-04-01','ACTIVE');</t>
+          <t>INSERT INTO users(email,password_hash,name,role,department_id,manager_id,hire_date,status) VALUES ('admin@example.com','$2a$10$DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD','人事 管理者','ADMIN',(SELECT id FROM departments WHERE name='管理部'),NULL,DATE '2024-04-01','ACTIVE');</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO users(email,password_hash,name,role,department_id,manager_id,hire_date,status) VALUES ('manager@example.com','$2a$10$DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD','佐藤 一郎','MANAGER',(SELECT id FROM departments WHERE name='営業部'),NULL,DATE '2024-04-01','ACTIVE');</t>
+          <t>INSERT INTO users(email,password_hash,name,role,department_id,manager_id,hire_date,status) VALUES ('manager@example.com','$2a$10$DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD','佐藤 一郎','MANAGER',(SELECT id FROM departments WHERE name='システム開発事業部'),NULL,DATE '2024-04-01','ACTIVE');</t>
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
@@ -1110,7 +1110,7 @@
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10" t="n"/>
     </row>
-    <row r="16" ht="34" customHeight="1">
+    <row r="16" ht="48.5" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>3</t>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO users(email,password_hash,name,role,department_id,manager_id,hire_date,status) VALUES ('taro@example.com','$2a$10$DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD','山田 太郎','EMPLOYEE',(SELECT id FROM departments WHERE name='営業部'),(SELECT id FROM users WHERE email='manager@example.com'),DATE '2024-04-01','ACTIVE');</t>
+          <t>INSERT INTO users(email,password_hash,name,role,department_id,manager_id,hire_date,status) VALUES ('taro@example.com','$2a$10$DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD','山田 太郎','EMPLOYEE',(SELECT id FROM departments WHERE name='システム開発事業部'),(SELECT id FROM users WHERE email='manager@example.com'),DATE '2024-04-01','ACTIVE');</t>
         </is>
       </c>
       <c r="C16" s="9" t="n"/>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO users(email,password_hash,name,role,department_id,manager_id,hire_date,status) VALUES ('hanako@example.com','$2a$10$DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD','鈴木 花子','EMPLOYEE',(SELECT id FROM departments WHERE name='営業部'),(SELECT id FROM users WHERE email='manager@example.com'),DATE '2024-04-01','ACTIVE');</t>
+          <t>INSERT INTO users(email,password_hash,name,role,department_id,manager_id,hire_date,status) VALUES ('hanako@example.com','$2a$10$DDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDDD','鈴木 花子','EMPLOYEE',(SELECT id FROM departments WHERE name='システム開発事業部'),(SELECT id FROM users WHERE email='manager@example.com'),DATE '2024-04-01','ACTIVE');</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
@@ -1426,7 +1426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F37"/>
+  <dimension ref="A2:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1 は編集せず、列追加・索引追加は V2__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -1605,357 +1605,357 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="77.5" customHeight="1">
+    <row r="13" ht="48.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
+          <t>C-4</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>PK 制約名が未指定で命名規約と不統一</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="77.5" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>C-5</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>業務ルールの CHECK 制約が少ない</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="63" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>C-6</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48.5" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>U-2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>上長の自己参照・循環を DB で防げない</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>users.manager_id は自己参照 FK。manager_id = id や循環（A→B→A）は ONL-014 のアプリ判定のみ。</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>手動 SQL で循環を作ると承認ルートが成立しない。</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>CHECK (manager_id IS NULL OR manager_id &lt;&gt; id) を追加。循環は 10章の再帰 CTE で定期検査。</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="77.5" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>U-4</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>email の小文字化を DB が強制しない</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>保存時の小文字化はアプリの責務で、DB に CHECK も LOWER(email) の一意索引も無い。アプリを経由しない手動 SQL や将来の別入口では大文字混じりのメールが入り、uq_users_1 では大文字小文字違いの重複を防げない。</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>大文字混じりのメールはログインに一致しなくなる（検索は小文字）。</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>CHECK (email = LOWER(email))（ck_users_email_lower）を追加。事前に 10章『大文字・前後空白を含むメール』が 0 行であることを確認。</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>題名</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>解消内容</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>根拠（DDL／規格）</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>残る事項</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="106.5" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>updated_at が更新時に自動更新されない</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="92" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>C-2</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="135.5" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
           <t>C-3</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48.5" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>C-4</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>PK 制約名が未指定で命名規約と不統一</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="77.5" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>C-5</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>業務ルールの CHECK 制約が少ない</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="63" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>C-6</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48.5" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>U-2</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>上長の自己参照・循環を DB で防げない</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>users.manager_id は自己参照 FK。manager_id = id や循環（A→B→A）は ONL-014 のアプリ判定のみ。</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>手動 SQL で循環を作ると承認ルートが成立しない。</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>CHECK (manager_id IS NULL OR manager_id &lt;&gt; id) を追加。循環は 10章の再帰 CTE で定期検査。</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="48.5" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="121" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>U-1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>メールアドレスの大文字小文字の扱いが処理間で不一致</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>保存・検索とも trim＋toLowerCase(Locale.ROOT) で正規化（ONL-001 は AuthService#login 内で実施済み。EmailNormalizer クラスは未実装で、ONL-014 実装時に共通化）。ONL-001 は正規化後の完全一致、ONL-014 の重複確認も UPPER() 比較をやめて正規化後の完全一致（uq_users_1 の索引が効く）。既存データは UPDATE users SET email = LOWER(TRIM(email)); で一度だけ移行（運用章）。</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>DB が小文字を強制していない（課題 U-4）。</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>users</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="92" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>U-3</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>ログイン失敗回数・パスワード変更日などの列が無い</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>ONL-001「未対応（今後）」：連続失敗ロック・ログイン履歴・トークン失効。ONL-014「初回ログイン時のパスワード強制変更」も未対応。</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>総当たり攻撃対策・パスワード期限管理ができない。無効化・ロール変更が発行済み JWT（最大 8 時間）に即時反映されない。</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>必要時に failed_login_count / locked_until / password_changed_at / token_version を追加（要 ALTER とマイグレーション）。</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="77.5" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>U-4</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>email の小文字化を DB が強制しない</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>保存時の小文字化はアプリ（EmailNormalizer）の責務で、DB に CHECK も LOWER(email) の一意索引も無い。アプリを経由しない手動 SQL や将来の別入口では大文字混じりのメールが入り、uq_users_1 では大文字小文字違いの重複を防げない。</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>大文字混じりのメールはログインに一致しなくなる（検索は小文字）。</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>CHECK (email = LOWER(email))（ck_users_email_lower）を追加。事前に 10章『大文字・前後空白を含むメール』が 0 行であることを確認。</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>題名</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>解消内容</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>根拠（DDL／規格）</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>残る事項</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="106.5" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>C-1</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>updated_at が更新時に自動更新されない</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="92" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>C-2</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="106.5" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>U-1</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>メールアドレスの大文字小文字の扱いが処理間で不一致</t>
-        </is>
-      </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>保存・検索とも EmailNormalizer#normalize（trim＋toLowerCase(Locale.ROOT)）で正規化。ONL-001 は正規化後の完全一致、ONL-014 の重複確認も UPPER() 比較をやめて正規化後の完全一致（uq_users_1 の索引が効く）。既存データは UPDATE users SET email = LOWER(TRIM(email)); で一度だけ移行（運用章）。</t>
+          <t>users に failed_login_count（INT 既定 0）・locked_until（TIMESTAMP）・must_change_password（BOOLEAN 既定 FALSE）・password_changed_at（TIMESTAMP）を追加（V1）。ONL-001 が 5 回失敗で 30 分ロック（E-017）、ONL-023 がパスワード変更で must_change_password を false にする。</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>DB が小文字を強制していない（課題 U-4）。</t>
+          <t>token_version（トークン失効）は未追加。無効化・ロール変更は発行済み JWT（最大 2 時間）に即時反映されない。管理者によるロック手動解除・サーバー側での mustChangePassword 強制は未実装。</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>連続失敗によるロック／ログイン履歴／トークン失効（ログアウト時の無効化）。※ 期限切れ・不正トークン時の JSON 形式の 401 応答は RestAuthenticationEntryPoint で対応済み。</t>
+          <t>ログイン履歴（監査ログ）／トークン失効（ログアウト時の無効化）／管理者によるロック解除操作（現状は 30 分経過で自動解除。locked_until を DB で NULL にすれば手動解除可）。</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限8時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更・承認待ち申請の承認者付け替え。</t>
+          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限2時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更のサーバー側実施（画面側は ONL-023 で実装済み）・承認待ち申請の承認者付け替え。</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
@@ -2181,14 +2181,75 @@
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
     </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約（総当たり）</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>現在のパスワード不一致（E-018）は failed_login_count に加算せずロックもしない。盗まれたトークンを使った総当たりを止める仕組みは、トークンの有効期間（2 時間）と BCrypt のコストのみ。必要なら E-018 の連続失敗もロック対象にする（後続改修案）。</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約（トークン失効なし）</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>パスワード変更後も、変更前に発行された JWT は有効期限（2 時間）まで使える。パスワード変更を契機にした全トークンの無効化は未実装（KF-RD-002 §4 のサーバー側失効は今後）。</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約（72 バイト）</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>@Size(max=72) は文字数の検査。BCrypt の入力上限は 72 バイトのため、全角文字などを含む長い新パスワードは 72 バイトを超え得る。超過した場合の挙動（先頭 72 バイトのみ有効／例外）は Spring Security のバージョンに依存するため、実装環境で確認する（未確認）。ASCII のみなら 72 文字が上限で問題なし。</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="24">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="C39:F39"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="C38:F38"/>
     <mergeCell ref="C32:F32"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="A2:F2"/>
@@ -2196,9 +2257,11 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="C40:F40"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
@@ -2483,7 +2546,7 @@
     <row r="13" ht="19.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -2519,7 +2582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2578,6 +2641,29 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="77.5" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql（Flyway）に移行し、users の 4 列（failed_login_count / locked_until / must_change_password / password_changed_at）を追加。ONL-001（ロック・E-017・JWT 2 時間）と ONL-023（パスワード変更）に追随。開発用ユーザーを 100 名に、課題 U-3・C-3 を解消済みへ更新。データ例を新しい部署名に変更。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2592,7 +2678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F44"/>
+  <dimension ref="A2:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2655,7 +2741,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway の V1__init_schema.sql（backend/src/main/resources/db/migration）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -2767,7 +2853,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>列 11 / 制約 6（PK 1・FK 2・UNIQUE 1・CHECK 2）/ 追加索引 2</t>
+          <t>列 15 / 制約 6（PK 1・FK 2・UNIQUE 1・CHECK 2）/ 追加索引 2</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -2865,7 +2951,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R/U</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -3191,25 +3277,25 @@
       <c r="E31" s="7" t="inlineStr"/>
       <c r="F31" s="10" t="n"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-023</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>年次有給休暇 自動付与</t>
+          <t>パスワード変更</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>バッチ</t>
+          <t>API-023 POST /api/auth/password</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R/U</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr"/>
@@ -3218,12 +3304,12 @@
     <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>BAT-002</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>年5日取得義務アラート</t>
+          <t>年次有給休暇 自動付与</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -3239,80 +3325,84 @@
       <c r="E33" s="7" t="inlineStr"/>
       <c r="F33" s="10" t="n"/>
     </row>
-    <row r="34" ht="34" customHeight="1">
+    <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>年5日取得義務アラート</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>バッチ</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>バッチ</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>pg_dump による全表読取（アプリ SQL なし）</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>1.3 関連設計書</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="10" t="n"/>
-    </row>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>文書番号</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>文書名</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>関連内容</t>
-        </is>
-      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
     </row>
     <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>KF-DD-003</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>テーブル設計書（総覧）</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>文書番号</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>文書名</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>関連内容</t>
         </is>
       </c>
       <c r="D38" s="9" t="n"/>
@@ -3322,17 +3412,17 @@
     <row r="39" ht="19.5" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-003</t>
+          <t>KF-DD-003</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>テーブル定義書（基本）</t>
+          <t>テーブル設計書（総覧）</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>論理名・基本項目</t>
+          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
@@ -3342,17 +3432,17 @@
     <row r="40" ht="19.5" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-005</t>
+          <t>KF-BD-003</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>コード定義書</t>
+          <t>テーブル定義書（基本）</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>コード値と状態遷移の基本設計</t>
+          <t>論理名・基本項目</t>
         </is>
       </c>
       <c r="D40" s="9" t="n"/>
@@ -3362,17 +3452,17 @@
     <row r="41" ht="19.5" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-001</t>
+          <t>KF-BD-005</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>オンライン設計書</t>
+          <t>コード定義書</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>ONL-001〜022 の概要</t>
+          <t>コード値と状態遷移の基本設計</t>
         </is>
       </c>
       <c r="D41" s="9" t="n"/>
@@ -3382,17 +3472,17 @@
     <row r="42" ht="19.5" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-ONL-xxx</t>
+          <t>KF-DD-001</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>オンライン詳細設計書</t>
+          <t>オンライン設計書</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>アクセスパターンの根拠（SQL・排他）</t>
+          <t>ONL-001〜022 の概要</t>
         </is>
       </c>
       <c r="D42" s="9" t="n"/>
@@ -3402,17 +3492,17 @@
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-004 / BAT</t>
+          <t>KF-DD-ONL-xxx</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>バッチ設計書</t>
+          <t>オンライン詳細設計書</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>BAT-001〜003 の使用</t>
+          <t>アクセスパターンの根拠（SQL・排他）</t>
         </is>
       </c>
       <c r="D43" s="9" t="n"/>
@@ -3422,25 +3512,45 @@
     <row r="44" ht="19.5" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>KF-DD-004 / BAT</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>DDL 本体</t>
+          <t>バッチ設計書</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>BAT-001〜003 の使用</t>
         </is>
       </c>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
       <c r="F44" s="10" t="n"/>
     </row>
+    <row r="45" ht="63" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>DDL 本体</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>本書の自動生成元</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
@@ -3448,11 +3558,12 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C37:F37"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E35:F35"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="E29:F29"/>
@@ -3465,6 +3576,7 @@
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C45:F45"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="E27:F27"/>
@@ -3475,7 +3587,6 @@
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="E32:F32"/>
-    <mergeCell ref="A36:F36"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="B5:F5"/>
@@ -3495,7 +3606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:M15"/>
+  <dimension ref="A2:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3516,7 +3627,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（V1__init_schema.sql から自動生成）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -3657,11 +3768,11 @@
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>使用ONL: 001, 005, 007, 008, 009, 010, 011, 012, 013, 014, 017, 018, 020, 022</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="77.5" customHeight="1">
+          <t>使用ONL: 001, 005, 007, 008, 009, 010, 011, 012, 013, 014, 017, 018, 020, 022, 023</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
@@ -3708,7 +3819,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>ONL-014 登録・変更時に管理者が入力。EmailNormalizer#normalize（trim＋toLowerCase(Locale.ROOT)）で正規化した小文字の値を保存する。ログインの検索キー（ONL-001）も同じ正規化後の値で完全一致検索する。</t>
+          <t>ONL-014 登録・変更時に管理者が入力。trim＋toLowerCase(Locale.ROOT) で正規化した小文字の値を保存する（EmailNormalizer クラスは未実装。ONL-014 実装時に共通化）。ログインの検索キー（ONL-001）も同じ正規化後の値で完全一致検索する。</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -3724,7 +3835,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.5" customHeight="1">
+    <row r="6" ht="121" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>3</v>
       </c>
@@ -3767,7 +3878,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>ONL-014 登録時（initialPassword）／パスワード設定（PUT /{id}/password）で BCrypt($2a$)ハッシュ化して保存。平文は保存しない。開発用 DevDataInitializer が seedPassword から 4 ユーザー分を設定。</t>
+          <t>ONL-014 登録時（initialPassword）／パスワード設定（PUT /{id}/password）で BCrypt($2a$)ハッシュ化して保存。平文は保存しない。開発用 DevDataInitializer が seedPassword から 100 ユーザー分を、BootstrapAdminInitializer が初期管理者 1 名分を設定。ONL-023（AuthService#changePassword）でも本人が変更する。</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -3778,7 +3889,7 @@
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>使用ONL: 001, 014</t>
+          <t>使用ONL: 001, 014, 023</t>
         </is>
       </c>
     </row>
@@ -4157,28 +4268,28 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="77.5" customHeight="1">
       <c r="A13" s="7" t="n">
         <v>10</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>ログイン失敗回数</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>failed_login_count</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>秒未満6桁</t>
+          <t>4バイト</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -4188,41 +4299,45 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>行の作成日時。</t>
+          <t>連続ログイン失敗回数。パスワード不一致で +1、5 回でロックして 0 に戻す。ログイン成功で 0 に戻す。</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>INSERT 時に DB の DEFAULT で設定（Entity は insertable=false）。</t>
+          <t>INSERT 時は DB の DEFAULT 0。ONL-001（AuthService#login）：パスワード不一致のたびに +1、5 回目に 0 へ戻して locked_until を設定、ログイン成功時に 0 へ戻す（0 でなければ UPDATE）。</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>createdAt
-LocalDateTime</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="inlineStr"/>
-    </row>
-    <row r="14" ht="121" customHeight="1">
+          <t>failedLoginCount
+int</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>使用ONL: 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="106.5" customHeight="1">
       <c r="A14" s="7" t="n">
         <v>11</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>ロック解除日時</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>locked_until</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -4237,57 +4352,285 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>CURRENT_TIMESTAMP</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="7" t="inlineStr"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
+          <t>アカウントのロック解除日時（JST）。NULL＝ロックなし。現在日時がこの日時より前ならロック中で、正しいパスワードでもログインできない。</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>ONL-001：5 回目の不一致で 現在日時（JST）＋30 分を設定。ログイン成功時（0 / NULL でなければ）NULL に戻す。ロック判定（現在日時より後ならロック中＝E-017）は ONL-001 のパスワード照合の前に行う。期限が過ぎれば自動的にロック解除（管理者による手動解除は未実装）。</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>lockedUntil
+LocalDateTime</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="inlineStr">
+        <is>
+          <t>使用ONL: 001</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="92" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>初期パスワード変更要否</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>must_change_password</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>初回のパスワード変更を求めるか。TRUE の間、画面はパスワード変更画面（SCR-007）から先へ進ませない。変更成功で FALSE。</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>INSERT 時は DB の DEFAULT FALSE。開発用ユーザー（DevDataInitializer）は FALSE、初期管理者（BootstrapAdminInitializer）は TRUE で作成。ONL-023 のパスワード変更成功で FALSE に更新。ログイン応答の mustChangePassword に返す。</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>mustChangePassword
+boolean</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>使用ONL: 001, 023</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="63" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>パスワード変更日時</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>password_changed_at</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>秒未満6桁</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>最後にパスワードを変更した日時（JST）。未変更は NULL。</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>INSERT 時は NULL。ONL-023（AuthService#changePassword）が成功時に現在日時（JST）を設定。ONL-014 のパスワード設定・初期投入では設定しない。</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>passwordChangedAt
+LocalDateTime</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>使用ONL: 023</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>秒未満6桁</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>行の作成日時。</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>INSERT 時に DB の DEFAULT で設定（Entity は insertable=false）。</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>createdAt
+LocalDateTime</t>
+        </is>
+      </c>
+      <c r="M17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="121" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>秒未満6桁</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
           <t>行の更新日時。UPDATE のたびに DB トリガ trg_users_updated_at が自動更新する（アプリは設定しない）。</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>INSERT 時は DB の DEFAULT。UPDATE 時は DB トリガ trg_users_updated_at（BEFORE UPDATE / set_updated_at）が現在日時（DB セッションの TimeZone＝Asia/Tokyo）へ自動更新する。アプリは設定しない（Entity は insertable=false, updatable=false）。ONL-014 の変更・無効化・パスワード設定でも更新される。</t>
         </is>
       </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>updatedAt
 LocalDateTime</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr"/>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="10" t="n"/>
+      <c r="M18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は V1__init_schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A19:M19"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A15:M15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -4315,7 +4658,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（V1__init_schema.sql の定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -4540,7 +4883,7 @@
       </c>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="77.5" customHeight="1">
+    <row r="11" ht="106.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>NOT NULL</t>
@@ -4553,7 +4896,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>email, password_hash, name, role, hire_date, status, created_at, updated_at</t>
+          <t>email, password_hash, name, role, hire_date, status, failed_login_count, must_change_password, created_at, updated_at</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -4568,7 +4911,7 @@
       </c>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="77.5" customHeight="1">
+    <row r="12" ht="121" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>DEFAULT</t>
@@ -4581,7 +4924,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>status='ACTIVE'; created_at=CURRENT_TIMESTAMP; updated_at=CURRENT_TIMESTAMP</t>
+          <t>status='ACTIVE'; failed_login_count=0; must_change_password=FALSE; created_at=CURRENT_TIMESTAMP; updated_at=CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -4668,16 +5011,16 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>○ ONL-005 申請者の行ロック  [先頭 1/1 列で絞込]  WHERE id = ?
+          <t>○ ONL-001 パスワード不一致時の失敗回数更新  [先頭 1/1 列で絞込]  WHERE id=?
+○ ONL-001 ログイン成功時の失敗回数リセット  [先頭 1/1 列で絞込]  WHERE id=?
+○ ONL-005 申請者の行ロック  [先頭 1/1 列で絞込]  WHERE id = ?
 ○ ONL-005 上長の取得／管理者一覧  [先頭 1/1 列で絞込]  WHERE id = ?
 ○ ONL-007 閲覧者・申請者・承認者  [先頭 1/1 列で絞込]  WHERE id = ?
-○ ONL-007 閲覧者・申請者・承認者  [先頭 1/1 列で絞込]  WHERE id IN (?, ?, ?)
-○ ONL-009 実行者の取得  [先頭 1/1 列で絞込]  WHERE id = ?
-ほか 13 件（id 指定の検索・更新・FK 検査）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="92" customHeight="1">
+ほか 17 件（id 指定の検索・更新・FK 検査）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="121" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
           <t>uq_users_1</t>
@@ -4707,11 +5050,12 @@
         <is>
           <t>○ ONL-001 ユーザー検索  [先頭 1/1 列で絞込]  WHERE email = ?
 ○ ONL-014 メール重複確認  [先頭 1/1 列で絞込]  WHERE email = ? [AND id &lt;&gt; ?]
-○ ONL-014 変更・無効化・パスワード設定  [先頭 1/1 列で絞込]  WHERE id=?</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="150" customHeight="1">
+○ ONL-014 変更・無効化・パスワード設定  [先頭 1/1 列で絞込]  WHERE id=?
+○ ONL-023 パスワード更新  [先頭 1/1 列で絞込]  WHERE id=?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="179" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
           <t>idx_users_manager</t>
@@ -4729,7 +5073,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>CREATE INDEX（schema.sql）</t>
+          <t>CREATE INDEX（V1__init_schema.sql）</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -4742,11 +5086,12 @@
           <t>○ ONL-014 部下の有無  [先頭 1/1 列で絞込]  WHERE manager_id = ? AND status = 'ACTIVE'
 ○ ONL-014 変更・無効化・パスワード設定  [先頭 1/1 列で絞込]  WHERE id=?
 ○ ONL-018 月次集計  [先頭 1/1 列で絞込]  WHERE work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL
-○ ONL-020 部下の月次集計  [先頭 1/1 列で絞込]  WHERE work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="164.5" customHeight="1">
+○ ONL-020 部下の月次集計  [先頭 1/1 列で絞込]  WHERE work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL
+○ ONL-023 パスワード更新  [先頭 1/1 列で絞込]  WHERE id=?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="193.5" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
           <t>idx_users_department</t>
@@ -4764,7 +5109,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>CREATE INDEX（schema.sql）</t>
+          <t>CREATE INDEX（V1__init_schema.sql）</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -4777,7 +5122,8 @@
           <t>△ ONL-014 一覧  [先頭 1/1 列で絞込]  WHERE (LOWER(name) LIKE LOWER('%'||?||'%') ESCAPE '\' OR LOWER(email) LIKE LOWER('%'||?||'%') ES
 ○ ONL-014 変更・無効化・パスワード設定  [先頭 1/1 列で絞込]  WHERE id=?
 ○ ONL-018 月次集計  [先頭 1/1 列で絞込]  WHERE work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL
-○ ONL-020 部下の月次集計  [先頭 1/1 列で絞込]  WHERE work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL</t>
+○ ONL-020 部下の月次集計  [先頭 1/1 列で絞込]  WHERE work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL
+○ ONL-023 パスワード更新  [先頭 1/1 列で絞込]  WHERE id=?</t>
         </is>
       </c>
     </row>
@@ -4892,7 +5238,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1__init_schema.sql＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B29" s="9" t="n"/>
@@ -5011,7 +5357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F17"/>
+  <dimension ref="A2:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5108,7 +5454,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>不可（ONL-001 が E-001）。ただし発行済み JWT は期限（8時間）まで有効</t>
+          <t>不可（ONL-001 が E-001）。ただし発行済み JWT は期限（2時間）まで有効</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -5245,7 +5591,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>4.3 users.role（ロール）</t>
+          <t>4.3 アカウントロックの状態（failed_login_count / locked_until）</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -5257,115 +5603,361 @@
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>コード</t>
+          <t>状態</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>failed_login_count</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>できること（概要）</t>
+          <t>locked_until</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="n"/>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>遷移のきっかけ</t>
+        </is>
+      </c>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>EMPLOYEE</t>
+          <t>通常</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>従業員</t>
+          <t>0〜4</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>自分の打刻・申請・残日数・通知</t>
+          <t>NULL（または過去日時）</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>承認不可、上長に指定不可</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="n"/>
+          <t>ログイン可（パスワードが正しければ）</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F15" s="10" t="n"/>
     </row>
-    <row r="16" ht="34" customHeight="1">
+    <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>MANAGER</t>
+          <t>失敗の積み上げ</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>上長</t>
+          <t>1〜4</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>EMPLOYEE の操作＋部下の申請の1段目承認、部下の勤怠一覧（ONL-020）</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>manager_id に指定できる</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="n"/>
+          <t>ログイン可。不一致ごとに +1</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>パスワード不一致（ONL-001）</t>
+        </is>
+      </c>
       <c r="F16" s="10" t="n"/>
     </row>
     <row r="17" ht="48.5" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>ロック中</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>現在日時より後（5 回目の失敗時刻＋30 分）</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>正しいパスワードでも E-017（HTTP 423）。ロック中の試行は回数に加算しない</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>5 回目のパスワード不一致</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>解除</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>過去日時（期限切れ）</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>通常どおりログイン可。成功時に locked_until を NULL に戻す</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>30 分経過（自動）。管理者による手動解除は未実装</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>4.4 must_change_password（初期パスワード変更要否）</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>設定する処理</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>画面側の扱い</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>初期パスワードのまま（変更が必要）</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer（初期管理者）</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>ログイン後 SCR-007 へ誘導し、変更が済むまで他画面へ進めない。サーバー側の強制は未実装</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>通常（既定）</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>既定値／DevDataInitializer／ONL-023 の成功時</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>通常どおり利用できる</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>4.5 users.role（ロール）</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>コード</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>できること（概要）</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>自分の打刻・申請・残日数・通知</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>承認不可、上長に指定不可</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>MANAGER</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>上長</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>EMPLOYEE の操作＋部下の申請の1段目承認、部下の勤怠一覧（ONL-020）</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>manager_id に指定できる</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="48.5" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t>ADMIN</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>管理者（人事）</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>最終（2段目）承認、ユーザー/休暇種別/祝日/付与の管理、月次集計（ONL-018）</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>ONL-020 は不可。上長にも指定可</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="24">
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="D23:F23"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="E18:F18"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -5821,7 +6413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J56"/>
+  <dimension ref="A2:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5893,12 +6485,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R/U</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>規格 tables：R ／ SQL 由来：R</t>
+          <t>規格 tables：R/U ／ SQL 由来：R/U</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
@@ -6272,25 +6864,25 @@
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="10" t="n"/>
     </row>
-    <row r="18" ht="34" customHeight="1">
+    <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-023</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>年次有給休暇 自動付与</t>
+          <t>パスワード変更</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R/U</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>BAT 詳細設計書の使用テーブル</t>
+          <t>規格 tables：R/U ／ SQL 由来：R/U</t>
         </is>
       </c>
       <c r="E18" s="9" t="n"/>
@@ -6303,12 +6895,12 @@
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>BAT-002</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>年5日取得義務アラート</t>
+          <t>年次有給休暇 自動付与</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -6331,12 +6923,12 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>BAT-003</t>
+          <t>BAT-002</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>データバックアップ（pg_dump）</t>
+          <t>年5日取得義務アラート</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -6356,151 +6948,131 @@
       <c r="I20" s="9" t="n"/>
       <c r="J20" s="10" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>BAT-003</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>データバックアップ（pg_dump）</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>BAT 詳細設計書の使用テーブル</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>6.2 アクセスパターン詳細（SQL 全文）</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>処理ID</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>処理名</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>操作</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>SQL 区分（規格のラベル）</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>SQL 全文</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>WHERE 条件</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>ORDER BY</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>想定件数</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>ロック</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>使用索引（○先頭列で絞込／△任意条件）</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>ONL-001</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>ログイン</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>ユーザー検索（UserRepository#findByEmail）</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users WHERE email = ?</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>email = ?</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>○uq_users_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48.5" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>申請作成</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>id = ?</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr"/>
@@ -6511,44 +7083,44 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>FOR UPDATE（悲観ロック）</t>
+          <t>なし（READ COMMITTED）</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>○users_pkey</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
+          <t>○uq_users_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48.5" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>申請作成</t>
+          <t>ログイン</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>上長の取得／管理者一覧</t>
+          <t>パスワード不一致時の失敗回数更新（UserRepository#save）</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE id = ?</t>
+          <t>UPDATE users SET failed_login_count=?, locked_until=? WHERE id=?</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>id = ?</t>
+          <t>id=?</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr"/>
@@ -6559,7 +7131,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>なし（READ COMMITTED）</t>
+          <t>行ロック（更新行に暗黙で取得）</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr">
@@ -6568,63 +7140,63 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
+    <row r="27" ht="63" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>申請作成</t>
+          <t>ログイン</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>上長の取得／管理者一覧</t>
+          <t>ログイン成功時の失敗回数リセット（UserRepository#save。値が変わる場合のみ）</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
+          <t>UPDATE users SET failed_login_count=0, locked_until=NULL WHERE id=?</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>role = 'ADMIN' AND status = 'ACTIVE'</t>
+          <t>id=?</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr"/>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>管理者数（数件）</t>
+          <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>なし（READ COMMITTED）</t>
+          <t>行ロック（更新行に暗黙で取得）</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>（索引なし／PK 結合）</t>
+          <t>○users_pkey</t>
         </is>
       </c>
     </row>
     <row r="28" ht="48.5" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>申請詳細取得</t>
+          <t>申請作成</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -6634,12 +7206,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>閲覧者・申請者・承認者（UserRepository#findById / findAllById）</t>
+          <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE id = ?</t>
+          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -6655,7 +7227,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>なし（READ COMMITTED）</t>
+          <t>FOR UPDATE（悲観ロック）</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -6664,15 +7236,15 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48.5" customHeight="1">
+    <row r="29" ht="34" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>申請詳細取得</t>
+          <t>申請作成</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -6682,17 +7254,17 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>閲覧者・申請者・承認者（UserRepository#findById / findAllById）</t>
+          <t>上長の取得／管理者一覧</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE id IN (?, ?, ?)</t>
+          <t>SELECT * FROM users WHERE id = ?</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>id IN (?, ?, ?)</t>
+          <t>id = ?</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr"/>
@@ -6712,15 +7284,15 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="48.5" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>ONL-008</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>申請取下げ</t>
+          <t>申請作成</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -6730,7 +7302,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>管理者の取得（2段目承認待ちのとき。UserRepository#findByRoleAndStatus）</t>
+          <t>上長の取得／管理者一覧</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
@@ -6760,15 +7332,15 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1">
+    <row r="31" ht="48.5" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>ONL-009</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>承認待ち一覧</t>
+          <t>申請詳細取得</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -6778,7 +7350,7 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>実行者の取得（UserRepository#findById）</t>
+          <t>閲覧者・申請者・承認者（UserRepository#findById / findAllById）</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -6808,28 +7380,172 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="280.5" customHeight="1">
+    <row r="32" ht="48.5" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>ONL-007</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>申請詳細取得</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>閲覧者・申請者・承認者（UserRepository#findById / findAllById）</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id IN (?, ?, ?)</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>id IN (?, ?, ?)</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48.5" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>ONL-008</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>申請取下げ</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>管理者の取得（2段目承認待ちのとき。UserRepository#findByRoleAndStatus）</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>role = 'ADMIN' AND status = 'ACTIVE'</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>管理者数（数件）</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>（索引なし／PK 結合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
           <t>ONL-009</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>承認待ち一覧</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>実行者の取得（UserRepository#findById）</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>id = ?</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="280.5" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>ONL-009</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>承認待ち一覧</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>承認待ちステップ検索（ApprovalStepRepository#findPending）</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>SELECT s.id, s.step_no, r.id, r.request_type, u.id, u.name, d.name,
        r.start_date, r.end_date, r.days, r.submitted_at, s1.acted_at
@@ -6845,160 +7561,16 @@
  ORDER BY r.submitted_at ASC, s.id ASC</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>s.status = 'WAITING' AND r.status = 'PENDING' AND r.current_step = s.step_no AND r.user_id &lt;&gt; :userId AND ((s.step_no = 1 AND s.approver_id = :userId) OR (s.step_no = 2 AND :admin = TRUE)) AND s.step_no IN (:stepNos) AND r.request_type IN (:types)</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>r.submitted_at ASC, s.id ASC</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>○users_pkey</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>承認</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>実行者・申請者の取得（UserRepository#findById）</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ?</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>id = ?</t>
-        </is>
-      </c>
-      <c r="G33" s="12" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>○users_pkey</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="63" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>ONL-010</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>承認</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>有効な管理者の取得（ApprovalRouteService#resolveCurrentApproverIds 内。ONL-005 定義・参考）</t>
-        </is>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>role = 'ADMIN' AND status = 'ACTIVE'</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>管理者数（数件）</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>（索引なし／PK 結合）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>ONL-011</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>差戻し</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>実行者の取得（UserRepository#findById）</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ?</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>id = ?</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr">
         <is>
           <t>0〜1 件（PK／一意キー）</t>
@@ -7018,12 +7590,12 @@
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>ONL-012</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>却下</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -7033,7 +7605,7 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>実行者の取得（UserRepository#findById）</t>
+          <t>実行者・申請者の取得（UserRepository#findById）</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
@@ -7063,15 +7635,15 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="34" customHeight="1">
+    <row r="37" ht="63" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>ONL-013</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>休暇残日数取得</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -7081,58 +7653,202 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>ユーザー取得（UserRepository#findById）</t>
+          <t>有効な管理者の取得（ApprovalRouteService#resolveCurrentApproverIds 内。ONL-005 定義・参考）</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE id = ?</t>
+          <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>id = ?</t>
+          <t>role = 'ADMIN' AND status = 'ACTIVE'</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr"/>
       <c r="H37" s="7" t="inlineStr">
         <is>
+          <t>管理者数（数件）</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>（索引なし／PK 結合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>ONL-011</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>差戻し</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>実行者の取得（UserRepository#findById）</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>id = ?</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
           <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>○users_pkey</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="92" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>ONL-012</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>却下</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>実行者の取得（UserRepository#findById）</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>id = ?</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>ONL-013</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>休暇残日数取得</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>ユーザー取得（UserRepository#findById）</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>id = ?</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="92" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>ONL-013</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>休暇残日数取得</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>義務期間内の年休付与行（BAT-002 用。LeaveBalanceRepository#findAlertBaseRows）</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>SELECT b.* FROM leave_balances b JOIN users u ON u.id = b.user_id
  WHERE u.status = 'ACTIVE' AND b.leave_type_id = ? AND b.granted_days &gt;= 10
@@ -7140,54 +7856,54 @@
  ORDER BY b.user_id, b.granted_on DESC, b.id DESC</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>u.status = 'ACTIVE' AND b.leave_type_id = ? AND b.granted_days &gt;= 10 AND b.granted_on &lt;= ? AND b.expires_on &gt;= ?</t>
         </is>
       </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>b.user_id, b.granted_on DESC, b.id DESC</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>○users_pkey</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="106.5" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="42" ht="106.5" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>ONL-014</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>ユーザー管理</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>一覧（UserRepository#search）</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users
  WHERE (LOWER(name) LIKE LOWER('%'||?||'%') ESCAPE '\' OR LOWER(email) LIKE LOWER('%'||?||'%') ESCAPE '\')
@@ -7195,173 +7911,29 @@
  ORDER BY id</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>(LOWER(name) LIKE LOWER('%'||?||'%') ESCAPE '\' OR LOWER(email) LIKE LOWER('%'||?||'%') ESCAPE '\') AND (? = '' OR role = ?) AND (? = '' OR status = ?) AND (? = 0 OR department_id = ?)</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>管理者数（数件）</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="J42" s="7" t="inlineStr">
         <is>
           <t>△idx_users_department</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>ONL-014</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>ユーザー管理</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>一覧（UserRepository#search）</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id IN (?, ...)</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>id IN (?, ...)</t>
-        </is>
-      </c>
-      <c r="G40" s="12" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>○users_pkey</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>ONL-014</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>ユーザー管理</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>対象の行ロック取得（findByIdForUpdate）</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>id = ?</t>
-        </is>
-      </c>
-      <c r="G41" s="12" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>FOR UPDATE（悲観ロック）</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>○users_pkey</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>ONL-014</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>ユーザー管理</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>メール重複確認</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>SELECT 1 FROM users WHERE email = ? [AND id &lt;&gt; ?] LIMIT 1</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>email = ? [AND id &lt;&gt; ?]</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
-        <is>
-          <t>○uq_users_1</t>
         </is>
       </c>
     </row>
@@ -7383,17 +7955,17 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>所属・上長の確認</t>
+          <t>一覧（UserRepository#search）</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE id = ?</t>
+          <t>SELECT * FROM users WHERE id IN (?, ...)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>id = ?</t>
+          <t>id IN (?, ...)</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr"/>
@@ -7431,199 +8003,343 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>部下の有無</t>
+          <t>対象の行ロック取得（findByIdForUpdate）</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>SELECT 1 FROM users WHERE manager_id = ? AND status = 'ACTIVE' LIMIT 1</t>
+          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>manager_id = ? AND status = 'ACTIVE'</t>
+          <t>id = ?</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr"/>
       <c r="H44" s="7" t="inlineStr">
         <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>FOR UPDATE（悲観ロック）</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>ONL-014</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>ユーザー管理</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>メール重複確認</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>SELECT 1 FROM users WHERE email = ? [AND id &lt;&gt; ?] LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>email = ? [AND id &lt;&gt; ?]</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>○uq_users_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>ONL-014</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>ユーザー管理</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>所属・上長の確認</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>id = ?</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>ONL-014</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>ユーザー管理</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>部下の有無</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>SELECT 1 FROM users WHERE manager_id = ? AND status = 'ACTIVE' LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>manager_id = ? AND status = 'ACTIVE'</t>
+        </is>
+      </c>
+      <c r="G47" s="12" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
           <t>部下数（数〜数十件）</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>○idx_users_manager</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="48.5" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="48" ht="48.5" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>ONL-014</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>ユーザー管理</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>登録（saveAndFlush）</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>INSERT INTO users(email, password_hash, name, role, department_id, manager_id, hire_date, status)
 VALUES (?, ?, ?, ?, ?, ?, ?, 'ACTIVE')</t>
         </is>
       </c>
-      <c r="F45" s="12" t="inlineStr"/>
-      <c r="G45" s="12" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr"/>
+      <c r="G48" s="12" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>1 件</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>なし</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>（索引なし／PK 結合）</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="63" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="49" ht="63" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>ONL-014</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>ユーザー管理</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>変更・無効化・パスワード設定（saveAndFlush）</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>UPDATE users SET email=?, password_hash=?, name=?, role=?, department_id=?, manager_id=?, hire_date=?, status=? WHERE id=?</t>
         </is>
       </c>
-      <c r="F46" s="12" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>id=?</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>行ロック（更新行に暗黙で取得）</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>○users_pkey, ○uq_users_1, ○idx_users_manager, ○idx_users_department</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="48.5" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="50" ht="48.5" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>ONL-017</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>休暇付与</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>POST 従業員の取得・ロック（UserRepository#findByIdForUpdate）</t>
         </is>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
-      <c r="F47" s="12" t="inlineStr">
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>id = ?</t>
         </is>
       </c>
-      <c r="G47" s="12" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="G50" s="12" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>FOR UPDATE（悲観ロック）</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="J50" s="7" t="inlineStr">
         <is>
           <t>○users_pkey</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="409" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="51" ht="409" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>ONL-018</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>月次集計取得</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>月次集計（ReportRepository#findMonthlySummary。ONL-020 と共用）</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>SELECT u.id,
        u.name,
@@ -7654,54 +8370,54 @@
 ORDER BY CASE WHEN u.department_id IS NULL THEN 1 ELSE 0 END, u.department_id, u.id</t>
         </is>
       </c>
-      <c r="F48" s="12" t="inlineStr">
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL</t>
         </is>
       </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="G51" s="12" t="inlineStr">
         <is>
           <t>CASE WHEN u.department_id IS NULL THEN 1 ELSE 0 END, u.department_id, u.id</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>部下数（数〜数十件）</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>○idx_users_manager, ○idx_users_department</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="409" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="52" ht="409" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>ONL-020</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>上長の部下一覧</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>部下の月次集計（ReportRepository#findMonthlySummary。ONL-018 と同一文。バインド値：departmentId=NULL、managerId=ログイン上長の ID）</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>SELECT u.id,
        u.name,
@@ -7732,225 +8448,89 @@
 ORDER BY CASE WHEN u.department_id IS NULL THEN 1 ELSE 0 END, u.department_id, u.id</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>work_date BETWEEN :fromDate AND :toDate AND clock_in IS NOT NULL</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>CASE WHEN u.department_id IS NULL THEN 1 ELSE 0 END, u.department_id, u.id</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>部下数（数〜数十件）</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>○idx_users_manager, ○idx_users_department</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="48.5" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="53" ht="48.5" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>ONL-022</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>申請提出</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>id = ?</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="G53" s="12" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>FOR UPDATE（悲観ロック）</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>○users_pkey</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>ONL-022</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>申請提出</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>上長の取得／管理者一覧（ApprovalRouteService）</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ?</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>id = ?</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>0〜1 件（PK／一意キー）</t>
-        </is>
-      </c>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>○users_pkey</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="34" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>ONL-022</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>申請提出</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>上長の取得／管理者一覧（ApprovalRouteService）</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>role = 'ADMIN' AND status = 'ACTIVE'</t>
-        </is>
-      </c>
-      <c r="G52" s="12" t="inlineStr"/>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>管理者数（数件）</t>
-        </is>
-      </c>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>（索引なし／PK 結合）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>BAT-001</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>年次有給休暇 自動付与</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>② 候補ユーザーの抽出（findGrantCandidates）</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
-        <is>
-          <t>SELECT u.id, u.hire_date FROM users u WHERE u.status = 'ACTIVE' AND u.hire_date &lt;= ? ORDER BY u.id</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr"/>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>（バッチ 1 回あたり：対象者数に比例）</t>
-        </is>
-      </c>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>なし（READ COMMITTED）</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr"/>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-022</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>年次有給休暇 自動付与</t>
+          <t>申請提出</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -7960,91 +8540,323 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>③ ユーザー行ロック（findByIdForUpdate）</t>
+          <t>上長の取得／管理者一覧（ApprovalRouteService）</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr"/>
-      <c r="G54" s="7" t="inlineStr"/>
+          <t>SELECT * FROM users WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>id = ?</t>
+        </is>
+      </c>
+      <c r="G54" s="12" t="inlineStr"/>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>（バッチ 1 回あたり：対象者数に比例）</t>
+          <t>0〜1 件（PK／一意キー）</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>FOR UPDATE（悲観ロック）</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr"/>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>申請提出</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>上長の取得／管理者一覧（ApprovalRouteService）</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>role = 'ADMIN' AND status = 'ACTIVE'</t>
+        </is>
+      </c>
+      <c r="G55" s="12" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>管理者数（数件）</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>（索引なし／PK 結合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>ユーザー取得（UserRepository#findById）</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>id = ?</t>
+        </is>
+      </c>
+      <c r="G56" s="12" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="77.5" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>パスワード更新（UserRepository#save）</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>UPDATE users SET email=?, password_hash=?, name=?, role=?, department_id=?, manager_id=?, hire_date=?, status=?, failed_login_count=?, locked_until=?, must_change_password=false, password_changed_at=? WHERE id=?</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>id=?</t>
+        </is>
+      </c>
+      <c r="G57" s="12" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>0〜1 件（PK／一意キー）</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>行ロック（更新行に暗黙で取得）</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>○users_pkey, ○uq_users_1, ○idx_users_manager, ○idx_users_department</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="34" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>BAT-001</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>年次有給休暇 自動付与</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>② 候補ユーザーの抽出（findGrantCandidates）</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>SELECT u.id, u.hire_date FROM users u WHERE u.status = 'ACTIVE' AND u.hire_date &lt;= ? ORDER BY u.id</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>（バッチ 1 回あたり：対象者数に比例）</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>なし（READ COMMITTED）</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>BAT-001</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>年次有給休暇 自動付与</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>③ ユーザー行ロック（findByIdForUpdate）</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>（バッチ 1 回あたり：対象者数に比例）</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>FOR UPDATE（悲観ロック）</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
           <t>BAT-002</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>年5日取得義務アラート</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>③ 全管理者（findByRoleAndStatus）</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>（バッチ 1 回あたり：対象者数に比例）</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>なし（READ COMMITTED）</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>※ 想定件数・使用索引はクエリ条件から機械的に推定した目安。Hibernate が発行する SQL は列を全て列挙する（SELECT * と表記）。BAT-003 は pg_dump（COPY）による全件読取のためこの表では省略。</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="10" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="D18:J18"/>
     <mergeCell ref="D3:J3"/>
     <mergeCell ref="D9:J9"/>
-    <mergeCell ref="A22:J22"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="D8:J8"/>
     <mergeCell ref="D15:J15"/>
@@ -8053,11 +8865,12 @@
     <mergeCell ref="D20:J20"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D19:J19"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="D21:J21"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D11:J11"/>
     <mergeCell ref="D17:J17"/>
-    <mergeCell ref="A56:J56"/>
     <mergeCell ref="D7:J7"/>
     <mergeCell ref="D16:J16"/>
     <mergeCell ref="A2:J2"/>
@@ -8074,7 +8887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F19"/>
+  <dimension ref="A2:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8145,15 +8958,15 @@
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="10" t="n"/>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>ロック順序</t>
+          <t>ログイン失敗回数の競合</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>users → requests → approval_steps → notifications（ONL-005）、users → leave_balances（ONL-017）。逆順に取らないこと。</t>
+          <t>ONL-001 の失敗回数更新は FOR UPDATE なしの読み取り→+1→保存のため、同一ユーザーへの同時のログイン失敗が重なると加算が 1 回分失われうる（5 回ロックが 6 回目になることがある）。実害は小さいため許容（行ロックを取る場合は findByIdForUpdate を使う）。</t>
         </is>
       </c>
       <c r="C6" s="9" t="n"/>
@@ -8164,12 +8977,12 @@
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>トランザクション注意</t>
+          <t>ロック順序</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>FOR UPDATE は @Transactional 内でのみ有効。readOnly トランザクションで users を FOR UPDATE しない。</t>
+          <t>users → requests → approval_steps → notifications（ONL-005）、users → leave_balances（ONL-017）。逆順に取らないこと。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -8177,61 +8990,53 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>トランザクション注意</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>FOR UPDATE は @Transactional 内でのみ有効。readOnly トランザクションで users を FOR UPDATE しない。</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>7.2 FOR UPDATE を使う処理（アクセスパターンから自動抽出）</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>処理名</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>SQL 区分</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>ONL-005</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>申請作成</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
+    <row r="11" ht="19.5" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>処理名</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>SQL 区分</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
         </is>
       </c>
       <c r="E11" s="9" t="n"/>
@@ -8240,17 +9045,17 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>ユーザー管理</t>
+          <t>申請作成</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>対象の行ロック取得（findByIdForUpdate）</t>
+          <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -8264,17 +9069,17 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>ONL-017</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>休暇付与</t>
+          <t>ユーザー管理</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>POST 従業員の取得・ロック（UserRepository#findByIdForUpdate）</t>
+          <t>対象の行ロック取得（findByIdForUpdate）</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8288,17 +9093,17 @@
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-017</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>申請提出</t>
+          <t>休暇付与</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
+          <t>POST 従業員の取得・ロック（UserRepository#findByIdForUpdate）</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -8309,43 +9114,51 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>ONL-022</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>申請提出</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>7.3 共通前提</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>分離レベル</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>READ COMMITTED（PostgreSQL 既定）。更新の競合は行ロック（FOR UPDATE）または条件付き UPDATE の更新件数で検出する。@Version（楽観ロック）用の列はどの表にも無い。</t>
-        </is>
-      </c>
+      <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="10" t="n"/>
     </row>
-    <row r="18" ht="34" customHeight="1">
+    <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>ロック順序（デッドロック防止）</t>
+          <t>分離レベル</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>users → requests → approval_steps → leave_balances / attendance_records → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一）。</t>
+          <t>READ COMMITTED（PostgreSQL 既定）。更新の競合は行ロック（FOR UPDATE）または条件付き UPDATE の更新件数で検出する。@Version（楽観ロック）用の列はどの表にも無い。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -8353,15 +9166,15 @@
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="10" t="n"/>
     </row>
-    <row r="19" ht="19.5" customHeight="1">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>ロック待ち</t>
+          <t>ロック順序（デッドロック防止）</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>バッチは lock.timeout=5000ms（BAT-001 D-8）。オンラインは既定（待ち続ける）のためトランザクションを短く保つ。</t>
+          <t>users → requests → approval_steps → leave_balances / attendance_records → notifications の一方向。逆順で取得しない（ONL-005/008/010〜013/017 の規格で統一）。</t>
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
@@ -8369,24 +9182,41 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="10" t="n"/>
     </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>ロック待ち</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>バッチは lock.timeout=5000ms（BAT-001 D-8）。オンラインは既定（待ち続ける）のためトランザクションを短く保つ。</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="B6:F6"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A9:F9"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="D15:F15"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="D10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-01_users_ユーザー_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-01_users_ユーザー_テーブル詳細設計書.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち users を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.1 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.2 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
 章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
         </is>
       </c>
@@ -746,7 +746,7 @@
       <c r="J2" s="9" t="n"/>
       <c r="K2" s="10" t="n"/>
     </row>
-    <row r="3" ht="63" customHeight="1">
+    <row r="3" ht="77.5" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>前提</t>
@@ -754,8 +754,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>dev の初期ユーザー（DevDataInitializer が 100 名を userRepository.count() = 0 かつ seed-password 設定時だけ作成）のうち代表 4 名。全員 hire_date=2024-04-01、status=ACTIVE。パスワードハッシュは $2a$10$... のダミー。failed_login_count=0・locked_until=NULL・must_change_password=FALSE・password_changed_at=NULL は DB の既定値のため INSERT に含めない。
-例の INSERT は V1 適用直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>dev の初期ユーザー（DevDataInitializer が 100 名を userRepository.count() = 0 かつ seed-password 設定時だけ作成）のうち代表 4 名。メール・氏名・ロール・部署・上長は DevDataInitializer と同じ。hire_date は例示のため全員 2024-04-01 としている（実際のシードは 2016-04-01＋（連番×97 日 mod 3500 日）で人ごとに異なり、admin@ 2016-04-01、manager@ 2018-11-27、taro@ 2019-06-09、hanako@ 2019-09-14）。status=ACTIVE。パスワードハッシュは $2a$10$... のダミー。failed_login_count=0・locked_until=NULL・must_change_password=FALSE・password_changed_at=NULL は DB の既定値のため INSERT に含めない。
+例の INSERT は V1・V2 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -1426,7 +1426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F40"/>
+  <dimension ref="A2:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1 は編集せず、列追加・索引追加は V2__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1・V2（祝日の初期データ）は適用後に編集せず、列追加・索引追加は次の版 V3__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="63" customHeight="1">
+    <row r="15" ht="77.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>C-6</t>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1765,101 +1765,101 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="18" ht="135.5" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>U-5</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>開発用シードの実行条件がプロパティの有無だけで、Spring プロファイルで制限していない</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>DevDataInitializer・DevLeaveBalanceInitializer は @Profile を持たず、kintaiflow.dev.seed-password が空でないことだけで動く。この値は application-local.properties（Git 管理外。application.properties が optional で読み込む）または環境変数 KINTAIFLOW_DEV_SEED_PASSWORD（Docker Compose の .env の DEV_SEED_PASSWORD）で設定できる。作成は users が 0 件のとき（年休付与は leave_balances が 0 件のとき）に限る。</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>本番で users が空のまま seed-password を設定して初回起動すると、全員が同じパスワードの架空ユーザー 100 名（admin@example.com は ADMIN）が作られる。</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>本番では DEV_SEED_PASSWORD を空にして初回起動する（運用。.env.example も空欄）。コード側で @Profile の付与や本番での起動拒否を検討する（コード変更のため本書の範囲外）。確認 SQL：users の @example.com が 0 件であること。</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>題名</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>解消内容</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>根拠（DDL／規格）</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>残る事項</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="106.5" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22" ht="106.5" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>C-1</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>updated_at が更新時に自動更新されない</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="92" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>C-2</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -1876,152 +1876,164 @@
     <row r="23" ht="135.5" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>C-2</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="135.5" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>C-3</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="121" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25" ht="121" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>U-1</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>メールアドレスの大文字小文字の扱いが処理間で不一致</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>保存・検索とも trim＋toLowerCase(Locale.ROOT) で正規化（ONL-001 は AuthService#login 内で実施済み。EmailNormalizer クラスは未実装で、ONL-014 実装時に共通化）。ONL-001 は正規化後の完全一致、ONL-014 の重複確認も UPPER() 比較をやめて正規化後の完全一致（uq_users_1 の索引が効く）。既存データは UPDATE users SET email = LOWER(TRIM(email)); で一度だけ移行（運用章）。</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>DB が小文字を強制していない（課題 U-4）。</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="92" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26" ht="92" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>U-3</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>ログイン失敗回数・パスワード変更日などの列が無い</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>users に failed_login_count（INT 既定 0）・locked_until（TIMESTAMP）・must_change_password（BOOLEAN 既定 FALSE）・password_changed_at（TIMESTAMP）を追加（V1）。ONL-001 が 5 回失敗で 30 分ロック（E-017）、ONL-023 がパスワード変更で must_change_password を false にする。</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>token_version（トークン失効）は未追加。無効化・ロール変更は発行済み JWT（最大 2 時間）に即時反映されない。管理者によるロック手動解除・サーバー側での mustChangePassword 強制は未実装。</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>解消済み（v2.0）</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>9.3 ONL 規格が挙げた既知の制約・未対応（この表を使う処理の security 欄から抜粋）</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>処理ID</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>内容（原文抜粋）</t>
-        </is>
-      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="10" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>ONL-001</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>既知の制約</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>ユーザー不存在時は BCrypt 照合を行わないため、応答時間にわずかな差が出る（タイミング攻撃の余地）。学習用途のため現時点では許容。</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>処理ID</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>内容（原文抜粋）</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
-    <row r="30" ht="34" customHeight="1">
+    <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>ONL-001</t>
@@ -2029,12 +2041,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>未対応（今後）</t>
+          <t>既知の制約</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>ログイン履歴（監査ログ）／トークン失効（ログアウト時の無効化）／管理者によるロック解除操作（現状は 30 分経過で自動解除。locked_until を DB で NULL にすれば手動解除可）。</t>
+          <t>ユーザー不存在時は BCrypt 照合を行わないため、応答時間にわずかな差が出る（タイミング攻撃の余地）。学習用途のため現時点では許容。</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -2044,17 +2056,17 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>ONL-005</t>
+          <t>ONL-001</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>既知の制約</t>
+          <t>未対応（今後）</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
+          <t>ログイン履歴（監査ログ）／トークン失効（ログアウト時の無効化）／管理者によるロック解除操作（現状は 30 分経過で自動解除。locked_until を DB で NULL にすれば手動解除可）。</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
@@ -2064,7 +2076,7 @@
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>ONL-007</t>
+          <t>ONL-005</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2074,7 +2086,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>権限判定のためロールは users.role の最新値を参照するため、閲覧者が ADMIN でも承認者でもない場合は users を1回余分に読む。部署・種別の変更履歴は保持していないため、過去申請でも現在の名称で表示される。</t>
+          <t>承認ルート確定後に上長が変更されても既存申請の approver_id は変わらない。管理者が1人のみで、その管理者自身が申請すると承認者がいなくなる（運用で別の管理者を用意する）。通知は type / request_id を持つため、画面は requestId があれば SCR-106 の該当申請へ遷移する（ONL-019）。</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -2084,7 +2096,7 @@
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>ONL-008</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2094,7 +2106,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>取下げ日時は updated_at（DB トリガ）で参照できるが、取下げ者の個別記録はない（本人のみが取下げ可能なため申請者と同一）。DRAFT / RETURNED の取下げでは通知しない。承認済み（APPROVED）の申請の取消は本 API の対象外。</t>
+          <t>権限判定のためロールは users.role の最新値を参照するため、閲覧者が ADMIN でも承認者でもない場合は users を1回余分に読む。部署・種別の変更履歴は保持していないため、過去申請でも現在の名称で表示される。</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -2104,17 +2116,17 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-008</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>既知の制約（今後）</t>
+          <t>既知の制約</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
+          <t>取下げ日時は updated_at（DB トリガ）で参照できるが、取下げ者の個別記録はない（本人のみが取下げ可能なため申請者と同一）。DRAFT / RETURNED の取下げでは通知しない。承認済み（APPROVED）の申請の取消は本 API の対象外。</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
@@ -2124,17 +2136,17 @@
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>ONL-013</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>既知の制約</t>
+          <t>既知の制約（今後）</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>承認待ち申請が確保する日数は差し引かない（承認時に E-004 となる）。consume の内訳（どの行から何日引いたか）は記録しない。年5日は申請の start_date で期間判定する簡略化。used_days の更新時も updated_at は DB トリガ（BEFORE UPDATE / set_updated_at）で自動更新される。</t>
+          <t>承認・差戻し・却下の操作履歴を残す監査ログ、承認者の代理設定、1段目の上長が INACTIVE になった場合の代理承認、1名の管理者が全段を承認する運用の制限。有効な ADMIN がいない場合、2段目は誰も処理できない。</t>
         </is>
       </c>
       <c r="D35" s="9" t="n"/>
@@ -2144,7 +2156,7 @@
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-013</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2154,17 +2166,17 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限2時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更のサーバー側実施（画面側は ONL-023 で実装済み）・承認待ち申請の承認者付け替え。</t>
+          <t>承認待ち申請が確保する日数は差し引かない（承認時に E-004 となる）。consume の内訳（どの行から何日引いたか）は記録しない。年5日は申請の start_date で期間判定する簡略化。used_days の更新時も updated_at は DB トリガ（BEFORE UPDATE / set_updated_at）で自動更新される。</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="10" t="n"/>
     </row>
-    <row r="37" ht="48.5" customHeight="1">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2174,27 +2186,27 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
+          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限2時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更のサーバー側実施（画面側は ONL-023 で実装済み）・承認待ち申請の承認者付け替え。</t>
         </is>
       </c>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
     </row>
-    <row r="38" ht="34" customHeight="1">
+    <row r="38" ht="48.5" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>ONL-023</t>
+          <t>ONL-022</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>既知の制約（総当たり）</t>
+          <t>既知の制約</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>現在のパスワード不一致（E-018）は failed_login_count に加算せずロックもしない。盗まれたトークンを使った総当たりを止める仕組みは、トークンの有効期間（2 時間）と BCrypt のコストのみ。必要なら E-018 の連続失敗もロック対象にする（後続改修案）。</t>
+          <t>再提出で前回の承認履歴（差戻しコメントを含む）が削除される。下書きの内容を更新する API（PUT）は未定義のため、内容を直したい場合は新規申請になる（今後の課題）。上長が変更されていれば、再提出時の承認ルートは新しい上長で作り直される。管理者が 1 人のみで本人が申請者の場合は承認者がいなくなる（ONL-005 と同じ運用制約）。</t>
         </is>
       </c>
       <c r="D38" s="9" t="n"/>
@@ -2209,12 +2221,12 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>既知の制約（トークン失効なし）</t>
+          <t>既知の制約（総当たり）</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>パスワード変更後も、変更前に発行された JWT は有効期限（2 時間）まで使える。パスワード変更を契機にした全トークンの無効化は未実装（KF-RD-002 §4 のサーバー側失効は今後）。</t>
+          <t>現在のパスワード不一致（E-018）は failed_login_count に加算せずロックもしない。盗まれたトークンを使った総当たりを止める仕組みは、トークンの有効期間（2 時間）と BCrypt のコストのみ。必要なら E-018 の連続失敗もロック対象にする（後続改修案）。</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
@@ -2229,17 +2241,37 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>既知の制約（72 バイト）</t>
+          <t>既知の制約（トークン失効なし）</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>@Size(max=72) は文字数の検査。BCrypt の入力上限は 72 バイトのため、全角文字などを含む長い新パスワードは 72 バイトを超え得る。超過した場合の挙動（先頭 72 バイトのみ有効／例外）は Spring Security のバージョンに依存するため、実装環境で確認する（未確認）。ASCII のみなら 72 文字が上限で問題なし。</t>
+          <t>パスワード変更後も、変更前に発行された JWT は有効期限（2 時間）まで使える。パスワード変更を契機にした全トークンの無効化は未実装（KF-RD-002 §4 のサーバー側失効は今後）。</t>
         </is>
       </c>
       <c r="D40" s="9" t="n"/>
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>ONL-023</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>既知の制約（72 バイト）</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>@Size(max=72) は文字数の検査。BCrypt の入力上限は 72 バイトのため、全角文字などを含む長い新パスワードは 72 バイトを超え得る。超過した場合の挙動（先頭 72 バイトのみ有効／例外）は Spring Security のバージョンに依存するため、実装環境で確認する（未確認）。ASCII のみなら 72 文字が上限で問題なし。</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2247,19 +2279,19 @@
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C41:F41"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="A11:F11"/>
@@ -2280,7 +2312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F13"/>
+  <dimension ref="A2:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2327,7 +2359,7 @@
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="10" t="n"/>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="48.5" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -2345,7 +2377,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>初期状態は ADMIN/ACTIVE 1、MANAGER/ACTIVE 1、EMPLOYEE/ACTIVE 2</t>
+          <t>8章のデータだけなら ADMIN/ACTIVE 1、MANAGER/ACTIVE 1、EMPLOYEE/ACTIVE 2。開発用シード適用後は ADMIN 2、MANAGER 9、EMPLOYEE 89（計 100）</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
@@ -2495,7 +2527,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="48.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>8</t>
@@ -2503,17 +2535,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>所属部署なしの有効ユーザー</t>
+          <t>開発用シード由来のユーザー（@example.com）が残っていないこと（本番）</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SELECT id, email FROM users WHERE department_id IS NULL AND status='ACTIVE';</t>
+          <t>SELECT COUNT(*) AS example_users FROM users WHERE email LIKE '%@example.com';</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>運用判断（0 行が望ましい。ONL-018 の並びで末尾になる）</t>
+          <t>本番は 0。開発では 100（シード）。8章のデータだけなら 4。本番で 0 以外なら DEV_SEED_PASSWORD が設定されたまま起動した可能性があるため、該当ユーザーを INACTIVE にして原因を確認する</t>
         </is>
       </c>
       <c r="E11" s="9" t="n"/>
@@ -2527,40 +2559,89 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>updated_at トリガ trg_users_updated_at が存在し有効であること</t>
+          <t>初期パスワードのまま（変更待ち）のユーザー</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SELECT tgname, tgenabled FROM pg_trigger WHERE tgrelid = 'users'::regclass AND NOT tgisinternal;</t>
+          <t>SELECT id, email, role FROM users WHERE must_change_password AND status='ACTIVE' ORDER BY id;</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1 行（trg_users_updated_at、tgenabled = 'O'＝有効）。0 行だと updated_at が更新されない</t>
+          <t>新規登録・パスワード設定直後のユーザーだけ。長期間残るユーザーは未ログインの可能性（8章のデータでは 0 行）</t>
         </is>
       </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>所属部署なしの有効ユーザー</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>SELECT id, email FROM users WHERE department_id IS NULL AND status='ACTIVE';</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>運用判断（0 行が望ましい。ONL-018 の並びで末尾になる）</t>
+        </is>
+      </c>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="10" t="n"/>
     </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>updated_at トリガ trg_users_updated_at が存在し有効であること</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>SELECT tgname, tgenabled FROM pg_trigger WHERE tgrelid = 'users'::regclass AND NOT tgisinternal;</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1 行（trg_users_updated_at、tgenabled = 'O'＝有効）。0 行だと updated_at が更新されない</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ V2__seed_holidays.sql ＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D3:F3"/>
@@ -2568,6 +2649,7 @@
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="D10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2582,7 +2664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2664,6 +2746,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>コードと突合して修正。①must_change_password：ONL-014 の登録（UserService#create）と管理者のパスワード設定（resetPassword）も TRUE にする（従来は初期管理者のみと記載）②サーバー側の強制は実装済み（JWT クレーム mcp=true のトークンはパスワード変更 API 以外を E-019 で拒否。従来『未実装』）③管理者のパスワード設定が failed_login_count=0・locked_until=NULL にしロック解除を兼ねる④ONL-023 の現在パスワード不一致も失敗回数に数える⑤EmailNormalizer は実装済み（従来『未実装』）⑥開発用シードの入社日を実際の算出式に訂正（従来『全員 2024-04-01』）。4.6 初期ユーザーの作成契機、運用・確認 SQL（開発用シードの本番混入確認）、課題 U-5 を追加。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2678,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F45"/>
+  <dimension ref="A2:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2861,15 +2966,15 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Entity クラス</t>
+          <t>初期データ</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>com.example.kintaiflow.entity.User</t>
+          <t>V1・V2 の SQL では作らない。アプリ起動時に DevDataInitializer（開発用 100 名。seed-password 設定時のみ）／BootstrapAdminInitializer（本番の初期管理者 1 名。環境変数があるときのみ）が users が 0 件のときだけ作成する（4.6）。</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
@@ -2880,12 +2985,12 @@
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Entity クラス</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>repository.UserRepository（findByEmail / findByIdForUpdate / findByRoleAndStatus / search ほか）</t>
+          <t>com.example.kintaiflow.entity.User</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -2893,136 +2998,128 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>repository.UserRepository（findByEmail / findByIdForUpdate / findByRoleAndStatus / search ほか）</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>1.2 主な利用処理（オンライン処理・バッチ）</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>処理ID</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>処理名</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>API / 種別</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>備考（規格 tables の注記ほか）</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>ONL-001</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>ログイン</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>API-001 POST /api/auth/login</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>R/U</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>ONL-005</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>申請作成</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>API-005 POST /api/requests</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>（行ロック）</t>
         </is>
       </c>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>ONL-007</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>申請詳細取得</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>API-007 GET /api/requests/{id}</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="n"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>ONL-008</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>申請取下げ</t>
+          <t>申請詳細取得</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>API-008 POST /api/requests/{id}/withdraw</t>
+          <t>API-007 GET /api/requests/{id}</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -3036,17 +3133,17 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>ONL-009</t>
+          <t>ONL-008</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>承認待ち一覧</t>
+          <t>申請取下げ</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>API-009 GET /api/approvals/pending</t>
+          <t>API-008 POST /api/requests/{id}/withdraw</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -3060,17 +3157,17 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>ONL-010</t>
+          <t>ONL-009</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>承認待ち一覧</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>API-010 POST /api/approvals/{id}/approve</t>
+          <t>API-009 GET /api/approvals/pending</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -3084,17 +3181,17 @@
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>ONL-011</t>
+          <t>ONL-010</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>差戻し</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>API-011 POST /api/approvals/{id}/return</t>
+          <t>API-010 POST /api/approvals/{id}/approve</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -3108,17 +3205,17 @@
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>ONL-012</t>
+          <t>ONL-011</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>却下</t>
+          <t>差戻し</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>API-012 POST /api/approvals/{id}/reject</t>
+          <t>API-011 POST /api/approvals/{id}/return</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -3132,74 +3229,74 @@
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
+          <t>ONL-012</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>却下</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>API-012 POST /api/approvals/{id}/reject</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t>ONL-013</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>休暇残日数取得</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>API-013 GET /api/leave-balances</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>（hire_date、findAlertBaseRows では status）</t>
         </is>
       </c>
-      <c r="F26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="48.5" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="48.5" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>ONL-014</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>ユーザー管理</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>API-014 GET / POST / PUT /api/admin/users[/{id}[/password]]</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>C/R/U</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>ONL-017</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>休暇付与</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>API-017 GET/POST/PUT /api/admin/leave-grants[/{id}]</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr"/>
@@ -3208,17 +3305,17 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>ONL-018</t>
+          <t>ONL-017</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>月次集計取得</t>
+          <t>休暇付与</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>API-018 GET /api/admin/reports/monthly</t>
+          <t>API-017 GET/POST/PUT /api/admin/leave-grants[/{id}]</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -3232,17 +3329,17 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>ONL-018</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>上長の部下一覧</t>
+          <t>月次集計取得</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>API-020 GET /api/manager/subordinates/summary</t>
+          <t>API-018 GET /api/admin/reports/monthly</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -3256,17 +3353,17 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>ONL-022</t>
+          <t>ONL-020</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>申請提出</t>
+          <t>上長の部下一覧</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>API-022 POST /api/requests/{id}/submit</t>
+          <t>API-020 GET /api/manager/subordinates/summary</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -3280,46 +3377,46 @@
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>ONL-023</t>
+          <t>ONL-022</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>パスワード変更</t>
+          <t>申請提出</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>API-023 POST /api/auth/password</t>
+          <t>API-022 POST /api/requests/{id}/submit</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>R/U</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="10" t="n"/>
     </row>
-    <row r="33" ht="19.5" customHeight="1">
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>BAT-001</t>
+          <t>ONL-023</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>年次有給休暇 自動付与</t>
+          <t>パスワード変更</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>バッチ</t>
+          <t>API-023 POST /api/auth/password</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R/U</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
@@ -3328,12 +3425,12 @@
     <row r="34" ht="19.5" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>BAT-002</t>
+          <t>BAT-001</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>年5日取得義務アラート</t>
+          <t>年次有給休暇 自動付与</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -3349,80 +3446,84 @@
       <c r="E34" s="7" t="inlineStr"/>
       <c r="F34" s="10" t="n"/>
     </row>
-    <row r="35" ht="34" customHeight="1">
+    <row r="35" ht="19.5" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>BAT-002</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>年5日取得義務アラート</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>バッチ</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>バッチ</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>pg_dump による全表読取（アプリ SQL なし）</t>
         </is>
       </c>
-      <c r="F35" s="10" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>1.3 関連設計書</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="10" t="n"/>
-    </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>文書番号</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>文書名</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>関連内容</t>
-        </is>
-      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
       <c r="D38" s="9" t="n"/>
       <c r="E38" s="9" t="n"/>
       <c r="F38" s="10" t="n"/>
     </row>
     <row r="39" ht="19.5" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>KF-DD-003</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>テーブル設計書（総覧）</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>文書番号</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>文書名</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>関連内容</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
@@ -3432,17 +3533,17 @@
     <row r="40" ht="19.5" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-003</t>
+          <t>KF-DD-003</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>テーブル定義書（基本）</t>
+          <t>テーブル設計書（総覧）</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>論理名・基本項目</t>
+          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
         </is>
       </c>
       <c r="D40" s="9" t="n"/>
@@ -3452,17 +3553,17 @@
     <row r="41" ht="19.5" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-005</t>
+          <t>KF-BD-003</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>コード定義書</t>
+          <t>テーブル定義書（基本）</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>コード値と状態遷移の基本設計</t>
+          <t>論理名・基本項目</t>
         </is>
       </c>
       <c r="D41" s="9" t="n"/>
@@ -3472,17 +3573,17 @@
     <row r="42" ht="19.5" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-001</t>
+          <t>KF-BD-005</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>オンライン設計書</t>
+          <t>コード定義書</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>ONL-001〜022 の概要</t>
+          <t>コード値と状態遷移の基本設計</t>
         </is>
       </c>
       <c r="D42" s="9" t="n"/>
@@ -3492,17 +3593,17 @@
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-ONL-xxx</t>
+          <t>KF-DD-001</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>オンライン詳細設計書</t>
+          <t>オンライン設計書</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>アクセスパターンの根拠（SQL・排他）</t>
+          <t>ONL-001〜022 の概要</t>
         </is>
       </c>
       <c r="D43" s="9" t="n"/>
@@ -3512,56 +3613,72 @@
     <row r="44" ht="19.5" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-004 / BAT</t>
+          <t>KF-DD-ONL-xxx</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>バッチ設計書</t>
+          <t>オンライン詳細設計書</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>BAT-001〜003 の使用</t>
+          <t>アクセスパターンの根拠（SQL・排他）</t>
         </is>
       </c>
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
       <c r="F44" s="10" t="n"/>
     </row>
-    <row r="45" ht="63" customHeight="1">
+    <row r="45" ht="19.5" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
+          <t>KF-DD-004 / BAT</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>DDL 本体</t>
+          <t>バッチ設計書</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>BAT-001〜003 の使用</t>
         </is>
       </c>
       <c r="D45" s="9" t="n"/>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="10" t="n"/>
     </row>
+    <row r="46" ht="63" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>DDL 本体</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>本書の自動生成元</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="43">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="C38:F38"/>
     <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E17:F17"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="B12:F12"/>
@@ -3570,16 +3687,19 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="C42:F42"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E36:F36"/>
     <mergeCell ref="C41:F41"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="B9:F9"/>
@@ -3587,9 +3707,11 @@
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C43:F43"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C46:F46"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E21:F21"/>
@@ -3772,7 +3894,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="92" customHeight="1">
+    <row r="5" ht="106.5" customHeight="1">
       <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
@@ -3819,7 +3941,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>ONL-014 登録・変更時に管理者が入力。trim＋toLowerCase(Locale.ROOT) で正規化した小文字の値を保存する（EmailNormalizer クラスは未実装。ONL-014 実装時に共通化）。ログインの検索キー（ONL-001）も同じ正規化後の値で完全一致検索する。</t>
+          <t>ONL-014 登録・変更時に管理者が入力。trim＋toLowerCase(Locale.ROOT) で正規化した小文字の値を保存する（util.EmailNormalizer#normalize。ONL-014 の登録・変更・検索で使用）。ログインの検索キー（ONL-001）も同じ正規化後の値で完全一致検索する（AuthService#login は同じ処理を直接実装）。</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -3835,7 +3957,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="121" customHeight="1">
+    <row r="6" ht="135.5" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>3</v>
       </c>
@@ -3878,7 +4000,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>ONL-014 登録時（initialPassword）／パスワード設定（PUT /{id}/password）で BCrypt($2a$)ハッシュ化して保存。平文は保存しない。開発用 DevDataInitializer が seedPassword から 100 ユーザー分を、BootstrapAdminInitializer が初期管理者 1 名分を設定。ONL-023（AuthService#changePassword）でも本人が変更する。</t>
+          <t>ONL-014 登録時（initialPassword）／パスワード設定（PUT /{id}/password）で BCrypt($2a$)ハッシュ化して保存。平文は保存しない。開発用 DevDataInitializer が seedPassword（全員同じ初期パスワード。値は本書に記載しない）から 100 ユーザー分を、BootstrapAdminInitializer が初期管理者 1 名分を設定。ONL-023（AuthService#changePassword）でも本人が変更する。</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -4268,7 +4390,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="77.5" customHeight="1">
+    <row r="13" ht="164.5" customHeight="1">
       <c r="A13" s="7" t="n">
         <v>10</v>
       </c>
@@ -4311,7 +4433,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>INSERT 時は DB の DEFAULT 0。ONL-001（AuthService#login）：パスワード不一致のたびに +1、5 回目に 0 へ戻して locked_until を設定、ログイン成功時に 0 へ戻す（0 でなければ UPDATE）。</t>
+          <t>JPA 経由の INSERT は Entity の初期値 0 を設定（DB の DEFAULT 0 は運用 SQL など JPA を通さない INSERT で効く）。ONL-001（AuthService#login）：パスワード不一致のたびに +1、5 回目に 0 へ戻して locked_until を設定、ログイン成功時に 0 へ戻す（0 でなければ UPDATE）。ONL-023 の現在パスワード不一致も同じ規則で数え（registerFailure）、変更成功で 0 に戻す。ONL-014 の管理者によるパスワード設定（resetPassword）も 0 に戻す。</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -4326,7 +4448,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="106.5" customHeight="1">
+    <row r="14" ht="179" customHeight="1">
       <c r="A14" s="7" t="n">
         <v>11</v>
       </c>
@@ -4369,7 +4491,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>ONL-001：5 回目の不一致で 現在日時（JST）＋30 分を設定。ログイン成功時（0 / NULL でなければ）NULL に戻す。ロック判定（現在日時より後ならロック中＝E-017）は ONL-001 のパスワード照合の前に行う。期限が過ぎれば自動的にロック解除（管理者による手動解除は未実装）。</t>
+          <t>ONL-001：5 回目の不一致で 現在日時（JST）＋30 分を設定。ログイン成功時（0 / NULL でなければ）NULL に戻す。ロック判定（現在日時より後ならロック中＝E-017）は ONL-001 のパスワード照合の前に行う。期限が過ぎれば自動的にロック解除。管理者のパスワード設定（ONL-014 PUT /{id}/password。UserService#resetPassword）は failed_login_count=0・locked_until=NULL にするため、ロックの手動解除を兼ねる（専用の解除 API は無い）。ONL-023 もロック中は E-017 で拒否する。</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -4384,7 +4506,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="92" customHeight="1">
+    <row r="15" ht="179" customHeight="1">
       <c r="A15" s="7" t="n">
         <v>12</v>
       </c>
@@ -4427,7 +4549,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>INSERT 時は DB の DEFAULT FALSE。開発用ユーザー（DevDataInitializer）は FALSE、初期管理者（BootstrapAdminInitializer）は TRUE で作成。ONL-023 のパスワード変更成功で FALSE に更新。ログイン応答の mustChangePassword に返す。</t>
+          <t>DB の DEFAULT は FALSE だが、JPA 経由の INSERT は Entity の値を設定する。TRUE にする処理：ONL-014 のユーザー登録（UserService#create。初期パスワードは初回ログイン時に変更を強制）、ONL-014 の管理者によるパスワード設定（resetPassword。本人が変更するまで暫定扱い）、初期管理者（BootstrapAdminInitializer）。FALSE：開発用ユーザー（DevDataInitializer。Entity 既定値）、ONL-023 のパスワード変更成功時。ログイン応答の mustChangePassword と JWT クレーム mcp に反映する。</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -5238,7 +5360,7 @@
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1__init_schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1・V2＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B29" s="9" t="n"/>
@@ -5357,7 +5479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F29"/>
+  <dimension ref="A2:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5735,7 +5857,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>30 分経過（自動）。管理者による手動解除は未実装</t>
+          <t>30 分経過（自動）。または管理者のパスワード設定（ONL-014 resetPassword）で即時解除</t>
         </is>
       </c>
       <c r="F18" s="10" t="n"/>
@@ -5776,7 +5898,7 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="10" t="n"/>
     </row>
-    <row r="22" ht="34" customHeight="1">
+    <row r="22" ht="48.5" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -5784,17 +5906,17 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>初期パスワードのまま（変更が必要）</t>
+          <t>初期パスワード／管理者が設定した暫定パスワードのまま（変更が必要）</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>BootstrapAdminInitializer（初期管理者）</t>
+          <t>ONL-014 の登録、ONL-014 のパスワード設定（resetPassword）、BootstrapAdminInitializer（初期管理者）</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>ログイン後 SCR-007 へ誘導し、変更が済むまで他画面へ進めない。サーバー側の強制は未実装</t>
+          <t>ログイン後 SCR-007 へ誘導する。サーバー側でも JWT クレーム mcp=true のトークンはパスワード変更 API（/api/auth/password）以外を 403（E-019）で拒否する（SecurityConfig の PasswordChangeRequiredFilter）。ONL-023 は新しいトークンを再発行しないため、変更後は再ログインが必要</t>
         </is>
       </c>
       <c r="E22" s="9" t="n"/>
@@ -5808,12 +5930,12 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>通常（既定）</t>
+          <t>通常（DB の既定）</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>既定値／DevDataInitializer／ONL-023 の成功時</t>
+          <t>DevDataInitializer（開発用ユーザー）／ONL-023 の成功時</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -5932,27 +6054,156 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>4.6 初期ユーザーの作成契機（アプリ起動時。V1・V2 の SQL では users を作らない）</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>処理（実行順）</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>作成するユーザー</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>動作条件</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>must_change_password</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="193.5" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>DevDataInitializer（@Order 1）</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>開発用の架空ユーザー 100 名（管理部 10＋技術者 90）。代表アカウント admin@ / manager@ / taro@ / hanako@（@example.com）。全員同じ初期パスワード（BCrypt 化。値は application-local.properties の kintaiflow.dev.seed-password、または環境変数 KINTAIFLOW_DEV_SEED_PASSWORD。本書には記載しない）</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>seed-password が空でなく、かつ users が 0 件のときだけ。開発（local）専用で、本番では設定しない</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>hire_date は 2016-04-01＋（連番×97 日 mod 3500 日）。部署 ID 1〜5 を直接指定する（V1 の INSERT 順に依存）。KF-DD-003『初期データ・開発用シード』参照</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="77.5" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>BootstrapAdminInitializer（@Order 2）</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>初期管理者 1 名（氏名『システム管理者』、ADMIN、部署 ID 1＝管理部、hire_date は起動日）</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>環境変数 KINTAIFLOW_BOOTSTRAP_ADMIN_EMAIL / _PASSWORD が両方あり、users が 0 件のときだけ。パスワードが 12 文字以上・英数字のポリシーを満たさないと起動失敗</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>email は trim＋小文字化。DevDataInitializer が先に作った場合は何もしない</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>ONL-014 ユーザー登録</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>管理者が画面から 1 名ずつ登録</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>ADMIN の操作</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>通常運用ではこの経路で追加する</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="29">
     <mergeCell ref="D27:F27"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E35:F35"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E34:F34"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="D26:F26"/>
     <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E32:F32"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="E18:F18"/>
